--- a/docs/spiderman_1967_50_villain_chapter_plan_old.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan_old.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 Villain Plan" sheetId="1" r:id="R276e927aa7834875"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rc9df6acf4aeb4b34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" r:id="Rc030a180b1394daa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="4" r:id="R93ebc1a983ee405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanic Templates" sheetId="5" r:id="R49f3316edebf4b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Summary" sheetId="6" r:id="Rda35a6e7f0444502"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Audit" sheetId="7" r:id="R5f342452d088479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 Villain Plan" sheetId="1" r:id="R6def37d75b844459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Ree80dc5cbc17435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" r:id="R68df23cf07484c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="4" r:id="Re31326359d354cfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanic Templates" sheetId="5" r:id="Rb21e09e7b2cd4f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Summary" sheetId="6" r:id="R35fd017f12b445a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Audit" sheetId="7" r:id="Rad0e4af8c8704643"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13647,40 +13647,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="25" customFormat="1" ht="32.099998474121094" customHeight="1">
-      <x:c r="A1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Template</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Best For</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Basic Loop</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scoring Hook</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Difficulty Knob</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Good Reuse Targets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notes</x:t>
-        </x:is>
+      <x:c r="A1" s="6" t="str">
+        <x:v>Template</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Best For</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Basic Loop</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Scoring Hook</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Difficulty Knob</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Good Reuse Targets</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Notes</x:v>
       </x:c>
       <x:c r="H1" s="26" t="n"/>
       <x:c r="I1" s="26" t="n"/>
@@ -13700,40 +13686,26 @@
       <x:c r="W1" s="26" t="n"/>
     </x:row>
     <x:row r="2" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Limited flips</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mind control, stage tricks, precision villains</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Start with finite flips; correct shots add flips; zero flips ends/graces.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jackpots for completing stages with flips remaining.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reduce flip awards; add decoys; shrink windows.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blackwell, Koga, Noah Boddy mini-phase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Strong because player can cradle but every move matters.</x:t>
-        </x:is>
+      <x:c r="A2" s="11" t="str">
+        <x:v>Limited flips</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>Mind control, stage tricks, precision villains</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>Start with finite flips; correct shots add flips; zero flips ends/graces.</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Jackpots for completing stages with flips remaining.</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>Reduce flip awards; add decoys; shrink windows.</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>Blackwell, Koga, Noah Boddy mini-phase</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>Strong because player can cradle but every move matters.</x:v>
       </x:c>
       <x:c r="H2" s="8" t="n"/>
       <x:c r="I2" s="8" t="n"/>
@@ -13753,40 +13725,26 @@
       <x:c r="W2" s="8" t="n"/>
     </x:row>
     <x:row r="3" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Moving lit target</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fast villains, gunslingers, rhythm modes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lit shot moves across bank/targets; hit correct shot before it moves.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Correct shot jackpot; perfect streak bonus.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Move faster; add decoys; punish wrong target.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sandman, Fiddler, Cowboy, Jesse James Robot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Easy to understand and reusable.</x:t>
-        </x:is>
+      <x:c r="A3" s="11" t="str">
+        <x:v>Moving lit target</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>Fast villains, gunslingers, rhythm modes</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>Lit shot moves across bank/targets; hit correct shot before it moves.</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Correct shot jackpot; perfect streak bonus.</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>Move faster; add decoys; punish wrong target.</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>Sandman, Fiddler, Cowboy, Jesse James Robot</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>Easy to understand and reusable.</x:v>
       </x:c>
       <x:c r="H3" s="8" t="n"/>
       <x:c r="I3" s="8" t="n"/>
@@ -13806,40 +13764,26 @@
       <x:c r="W3" s="8" t="n"/>
     </x:row>
     <x:row r="4" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden correct shot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Illusions, invisible/disguise villains</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Several shots lit; only one is true; clues narrow possibilities.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True jackpot starts high and decays with wrong shots.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More decoys; clues less direct.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mysterio, Noah Boddy, Phantom, Cameo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Good for JJJ/Bugle clue callouts.</x:t>
-        </x:is>
+      <x:c r="A4" s="11" t="str">
+        <x:v>Hidden correct shot</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Illusions, invisible/disguise villains</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Several shots lit; only one is true; clues narrow possibilities.</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>True jackpot starts high and decays with wrong shots.</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>More decoys; clues less direct.</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Mysterio, Noah Boddy, Phantom, Cameo</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>Good for JJJ/Bugle clue callouts.</x:v>
       </x:c>
       <x:c r="H4" s="8" t="n"/>
       <x:c r="I4" s="8" t="n"/>
@@ -13859,40 +13803,26 @@
       <x:c r="W4" s="8" t="n"/>
     </x:row>
     <x:row r="5" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed delivery</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rescue, serum, fountain, underwater modes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect item, then deliver to lit destination before value decays.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Delivery jackpot based on time/value left.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Faster decay; extra delivery steps.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lizard, Doctor Manta, Ponce de León</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simple and satisfying.</x:t>
-        </x:is>
+      <x:c r="A5" s="11" t="str">
+        <x:v>Timed delivery</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Rescue, serum, fountain, underwater modes</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Collect item, then deliver to lit destination before value decays.</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Delivery jackpot based on time/value left.</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Faster decay; extra delivery steps.</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Lizard, Doctor Manta, Ponce de León</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>Simple and satisfying.</x:v>
       </x:c>
       <x:c r="H5" s="8" t="n"/>
       <x:c r="I5" s="8" t="n"/>
@@ -13912,40 +13842,26 @@
       <x:c r="W5" s="8" t="n"/>
     </x:row>
     <x:row r="6" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Area control</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monster/science/city attack modes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Several areas have meters; hits heat/thaw/repair/clear them.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Area jackpot when a meter completes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meters decay; hazards spread faster.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Parafino, Reptilla, Master Vine, Metal-Eating Monster</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Builds toward wizard area-clear logic.</x:t>
-        </x:is>
+      <x:c r="A6" s="11" t="str">
+        <x:v>Area control</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Monster/science/city attack modes</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Several areas have meters; hits heat/thaw/repair/clear them.</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Area jackpot when a meter completes.</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Meters decay; hazards spread faster.</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>Parafino, Reptilla, Master Vine, Metal-Eating Robot</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>Builds toward wizard area-clear logic.</x:v>
       </x:c>
       <x:c r="H6" s="8" t="n"/>
       <x:c r="I6" s="8" t="n"/>
@@ -13965,40 +13881,26 @@
       <x:c r="W6" s="8" t="n"/>
     </x:row>
     <x:row r="7" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Saucer trap / hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mole Man, Manta, Goblin-like traps</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Saucer holds or hides value; player finds/escapes/cashes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden saucer or held jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relocate faster; shorter hold windows.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mole Man, Doctor Manta, Blackbeard Robot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Remember to delay ejects where coils need recovery.</x:t>
-        </x:is>
+      <x:c r="A7" s="11" t="str">
+        <x:v>Saucer trap / hold</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Mole Man, Manta, Goblin-like traps</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>Saucer holds or hides value; player finds/escapes/cashes.</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Hidden saucer or held jackpot.</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>Relocate faster; shorter hold windows.</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>Mole Man, Doctor Manta, Blackbeard Robot</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>Remember to delay ejects where coils need recovery.</x:v>
       </x:c>
       <x:c r="H7" s="8" t="n"/>
       <x:c r="I7" s="8" t="n"/>
@@ -14018,40 +13920,26 @@
       <x:c r="W7" s="8" t="n"/>
     </x:row>
     <x:row r="8" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Robot priority</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Robot attack and repair modes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Robot attacks a target group; player must hit priority shot before timer.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">System-disable jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shorter attack timer; more systems.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spider-Slayer, Smythe, historical robots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Good shared skeleton for Chapter 7.</x:t>
-        </x:is>
+      <x:c r="A8" s="11" t="str">
+        <x:v>Robot priority</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Robot attack and repair modes</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Robot attacks a target group; player must hit priority shot before timer.</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>System-disable jackpot.</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Shorter attack timer; more systems.</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>Spider-Slayer, Smythe, historical robots</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Good shared skeleton for Chapter 7.</x:v>
       </x:c>
       <x:c r="H8" s="8" t="n"/>
       <x:c r="I8" s="8" t="n"/>
@@ -14071,40 +13959,26 @@
       <x:c r="W8" s="8" t="n"/>
     </x:row>
     <x:row r="9" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Freeze/spread hazard</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Snow, vines, ink, curse, pressure</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hazard spreads or freezes shots; player clears before table is overrun.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Clear jackpot and rescue bonus.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spread faster; clear value decays.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Doctor Cool, Snowman, Master Vine, Blotto</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Useful visual mode family.</x:t>
-        </x:is>
+      <x:c r="A9" s="11" t="str">
+        <x:v>Freeze/spread hazard</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Snow, vines, ink, curse, pressure</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Hazard spreads or freezes shots; player clears before table is overrun.</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Clear jackpot and rescue bonus.</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>Spread faster; clear value decays.</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Doctor Cool, Snowman, Master Vine, Blotto</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>Useful visual mode family.</x:v>
       </x:c>
       <x:c r="H9" s="8" t="n"/>
       <x:c r="I9" s="8" t="n"/>
@@ -14124,40 +13998,26 @@
       <x:c r="W9" s="8" t="n"/>
     </x:row>
     <x:row r="10" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Paired shots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Twins, dual villains, synchronized attacks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hit two linked shots within a window.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Double jackpot for completed pair.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shorter pair window; moving pair.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fly Twins, Enforcers, chapter mini-wizards</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Creates satisfying left/right layout use.</x:t>
-        </x:is>
+      <x:c r="A10" s="11" t="str">
+        <x:v>Paired shots</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Twins, dual villains, synchronized attacks</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Hit two linked shots within a window.</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Double jackpot for completed pair.</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>Shorter pair window; moving pair.</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Fly Twins, Enforcers, chapter mini-wizards</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>Creates satisfying left/right layout use.</x:v>
       </x:c>
       <x:c r="H10" s="8" t="n"/>
       <x:c r="I10" s="8" t="n"/>
@@ -14177,40 +14037,26 @@
       <x:c r="W10" s="8" t="n"/>
     </x:row>
     <x:row r="11" s="25" customFormat="1" ht="78" customHeight="1">
-      <x:c r="A11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sequence plan</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Crime planning, investigations, rituals</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Follow a planned shot order; wrong shot resets or reduces value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blueprint/relic/lead jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Longer sequence; shorter preview.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Plotter, Foswell, Kotep, Dumpty</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simple rules, lots of theme flexibility.</x:t>
-        </x:is>
+      <x:c r="A11" s="11" t="str">
+        <x:v>Sequence plan</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>Crime planning, investigations, rituals</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Follow a planned shot order; wrong shot resets or reduces value.</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>Blueprint/relic/lead jackpot.</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>Longer sequence; shorter preview.</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>Plotter, Foswell, Kotep, Dumpty</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>Simple rules, lots of theme flexibility.</x:v>
       </x:c>
       <x:c r="H11" s="8" t="n"/>
       <x:c r="I11" s="8" t="n"/>
@@ -14230,40 +14076,26 @@
       <x:c r="W11" s="8" t="n"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rumour economy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Investigation/newspaper modes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops build a banked resource; spinner converts resource into saucer/headline progress; jackpots open VUK/gate.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Repeated supers and mode extension based on remaining resource.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Resource drains faster; conversion slots limited.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Foswell, Daily Bugle modes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Distinct from hidden reveal: player manages resource flow and headlines.</x:t>
-        </x:is>
+      <x:c r="A12" s="8" t="str">
+        <x:v>Rumour economy</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>Investigation/newspaper modes</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>Pops build a banked resource; spinner converts resource into saucer/headline progress; jackpots open VUK/gate.</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>Repeated supers and mode extension based on remaining resource.</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>Resource drains faster; conversion slots limited.</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="str">
+        <x:v>Foswell, Daily Bugle modes</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>Distinct from hidden reveal: player manages resource flow and headlines.</x:v>
       </x:c>
       <x:c r="H12" s="8" t="n"/>
       <x:c r="I12" s="8" t="n"/>
@@ -17755,7 +17587,7 @@
         <x:v>https://marvelanimated.fandom.com/wiki/Reptilla_(Spider-Man_(1967))</x:v>
       </x:c>
       <x:c r="F4" s="40" t="str">
-        <x:v>Lizard is Where Crawls the Lizard; Conner's Reptiles is Reptilla/Conner follow-up.</x:v>
+        <x:v>Lizard is Where Crawls the Lizard; Conner's Reptiles is Reptilla/Conner follo...</x:v>
       </x:c>
       <x:c r="G4" s="40" t="str">
         <x:v>High</x:v>
@@ -18206,7 +18038,7 @@
         <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
       </x:c>
       <x:c r="F15" s="40" t="str">
-        <x:v>Moved into Monsters; Vulcan appears in Here Comes Trubble as one of Miss Trubble's summoned figures.</x:v>
+        <x:v>Moved into Monsters; Vulcan appears in Here Comes Trubble as one of Miss Trub...</x:v>
       </x:c>
       <x:c r="G15" s="40" t="str">
         <x:v>High</x:v>
@@ -18288,7 +18120,7 @@
         <x:v>https://marvelanimated.fandom.com/wiki/Enforcers_(Spider-Man_(1967))</x:v>
       </x:c>
       <x:c r="F17" s="40" t="str">
-        <x:v>Enforcers/Ox grouping verified through Blueprint for Crime; Ox and Cowboy are Plotter's thieves.</x:v>
+        <x:v>Enforcers/Ox grouping verified through Blueprint for Crime; Ox and Cowboy are...</x:v>
       </x:c>
       <x:c r="G17" s="40" t="str">
         <x:v>High</x:v>
@@ -18358,7 +18190,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="40" t="str">
-        <x:v>Fifth Avenue Phantom</x:v>
+        <x:v>The Fifth Avenue Phantom</x:v>
       </x:c>
       <x:c r="C19" s="40" t="str">
         <x:v>Fifth Avenue Phantom / The Dark Terrors</x:v>
@@ -18411,7 +18243,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F20" s="40" t="str">
-        <x:v>Corrected: Frederick Foswell appears in King Pinned as Kingpin's Daily Bugle stooge in the 1967 series.</x:v>
+        <x:v>Corrected: Frederick Foswell appears in King Pinned as Kingpin's Daily Bugle ...</x:v>
       </x:c>
       <x:c r="G20" s="40" t="str">
         <x:v>High</x:v>
@@ -18534,7 +18366,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F23" s="40" t="str">
-        <x:v>Corrected: Doctor Manta is in Phantom from the Depths of Time, not Neptune's Nose Cone.</x:v>
+        <x:v>Corrected: Doctor Manta is in Phantom from the Depths of Time, not Neptune's ...</x:v>
       </x:c>
       <x:c r="G23" s="40" t="str">
         <x:v>High</x:v>
@@ -18645,7 +18477,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="40" t="str">
-        <x:v>Doctor Zapp</x:v>
+        <x:v>Doctor Zappp</x:v>
       </x:c>
       <x:c r="C26" s="40" t="str">
         <x:v>Spider-Man Meets Skyboy</x:v>
@@ -18657,7 +18489,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F26" s="40" t="str">
-        <x:v>Doctor Zapp verified as Skyboy episode villain.</x:v>
+        <x:v>Doctor Zappp verified as Skyboy episode villain.</x:v>
       </x:c>
       <x:c r="G26" s="40" t="str">
         <x:v>High</x:v>
@@ -18739,7 +18571,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F28" s="40" t="str">
-        <x:v>Kotep the Scarlet Sorcerer verified.</x:v>
+        <x:v>Kotep the Kotep verified.</x:v>
       </x:c>
       <x:c r="G28" s="40" t="str">
         <x:v>High</x:v>
@@ -18862,7 +18694,7 @@
         <x:v>https://marvelanimated.fandom.com/wiki/Reptilla_(Spider-Man_(1967))</x:v>
       </x:c>
       <x:c r="F31" s="40" t="str">
-        <x:v>Moved into Mystic Menace; Reptilla is the intelligent reptile/alligator creature from Conner's Reptiles.</x:v>
+        <x:v>Moved into Mystic Menace; Reptilla is the intelligent reptile/alligator creat...</x:v>
       </x:c>
       <x:c r="G31" s="40" t="str">
         <x:v>High</x:v>
@@ -19137,7 +18969,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="40" t="str">
-        <x:v>Metal-Eating Monster</x:v>
+        <x:v>Metal-Eating Robot</x:v>
       </x:c>
       <x:c r="C38" s="40" t="str">
         <x:v>Diet of Destruction</x:v>
@@ -19149,7 +18981,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F38" s="40" t="str">
-        <x:v>Metal-Eating Monster/robot verified.</x:v>
+        <x:v>Metal-Eating Robot/robot verified.</x:v>
       </x:c>
       <x:c r="G38" s="40" t="str">
         <x:v>High</x:v>
@@ -19272,7 +19104,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F41" s="40" t="str">
-        <x:v>Corrected: Pod belongs to Rollarama as giant rolling seed pods; best as phase/hazard, not full standalone villain.</x:v>
+        <x:v>Corrected: Pod belongs to Rollarama as giant rolling seed pods; best as phase...</x:v>
       </x:c>
       <x:c r="G41" s="40" t="str">
         <x:v>High</x:v>
@@ -19764,7 +19596,7 @@
         <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F53" s="40" t="str">
-        <x:v>Corrected: South Pole natives are in Neptune's Nose Cone; weak as standalone villain.</x:v>
+        <x:v>Corrected: South Pole natives are in Neptune's Nose Cone; weak as standalone ...</x:v>
       </x:c>
       <x:c r="G53" s="40" t="str">
         <x:v>High</x:v>
